--- a/EXCEL/Exercise Files/Chapter06/06_03_Expected Value.xlsx
+++ b/EXCEL/Exercise Files/Chapter06/06_03_Expected Value.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25407"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Curtis\Desktop\Exercise Files\Chapter06\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\neha work\Data Analytics\EXCEL\Exercise Files\Chapter06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A259E95-D587-4884-B09C-AB71BD7E2EE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F9A0983-4D06-4E0A-BEDB-46B49E4E114C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="12549" xr2:uid="{1F720F31-FEA7-4E3F-AA94-D608D435607B}"/>
+    <workbookView xWindow="288" yWindow="324" windowWidth="22752" windowHeight="11916" xr2:uid="{1F720F31-FEA7-4E3F-AA94-D608D435607B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -54,7 +53,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -108,15 +107,15 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -439,15 +438,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84E88D9B-DEC9-4A68-AEC3-AFE00B23C89F}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -461,7 +460,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -471,9 +470,12 @@
       <c r="C2" s="1">
         <v>50000</v>
       </c>
-      <c r="D2" s="1"/>
+      <c r="D2" s="1">
+        <f>B2*C2</f>
+        <v>12500</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -483,9 +485,12 @@
       <c r="C3" s="1">
         <v>-25000</v>
       </c>
-      <c r="D3" s="1"/>
+      <c r="D3" s="1">
+        <f t="shared" ref="D3:D4" si="0">B3*C3</f>
+        <v>-15000</v>
+      </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -495,9 +500,12 @@
       <c r="C4" s="1">
         <v>14000</v>
       </c>
-      <c r="D4" s="1"/>
+      <c r="D4" s="1">
+        <f t="shared" si="0"/>
+        <v>2100</v>
+      </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D5" s="3"/>
     </row>
   </sheetData>
